--- a/model runs/model_run_log.xlsx
+++ b/model runs/model_run_log.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bmgf-my.sharepoint.com/personal/anu_mishra_gatesfoundation_org/Documents/Documents/GitHub/CBHMIS_SAE_MMR/model runs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="8_{12758ECD-B819-44B8-B484-81DE156BF890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58B56488-B108-4C0D-BAE2-1EAEC40DF2AA}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="8_{12758ECD-B819-44B8-B484-81DE156BF890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB7B2B18-2E96-445C-8F21-9E960AA30FA0}"/>
   <bookViews>
-    <workbookView xWindow="1740" yWindow="105" windowWidth="21600" windowHeight="15330" xr2:uid="{F4D68F17-7C52-47C3-8064-6916CC3C0478}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{F4D68F17-7C52-47C3-8064-6916CC3C0478}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
   <si>
     <t>Model Run No</t>
   </si>
@@ -65,9 +65,6 @@
     <t>Removed ANC referral from reporting model</t>
   </si>
   <si>
-    <t>i</t>
-  </si>
-  <si>
     <t>This model seems to have issues because we estimate a negative relationship between ANC referral and underreporting. Assuming identifiability issues</t>
   </si>
   <si>
@@ -96,9 +93,6 @@
   </si>
   <si>
     <t>Fixed model stability keep changes moving forward</t>
-  </si>
-  <si>
-    <t>Slight inc</t>
   </si>
 </sst>
 </file>
@@ -488,7 +482,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEF5CF53-FD41-4752-A05E-5D5C66978713}">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.140625" customWidth="1"/>
@@ -497,7 +491,7 @@
     <col min="4" max="4" width="66" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -511,7 +505,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -522,7 +516,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -533,13 +527,10 @@
         <v>7</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -550,63 +541,60 @@
         <v>8</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
         <v>12</v>
       </c>
-      <c r="C5" t="s">
-        <v>13</v>
-      </c>
       <c r="D5" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>8</v>
       </c>
